--- a/data/trans_orig/IP74A5_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP74A5_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto los impuestos.. en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de los impuestos relacionados con vehículos, IBI, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>66,17%</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>835</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>93,12%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>563</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>66,2%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,73%</t>
         </is>
       </c>
     </row>
